--- a/AAII_Financials/Quarterly/SNPS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNPS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>SNPS</t>
   </si>
@@ -656,538 +656,550 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2476800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2276000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2408800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2254900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1739700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1604300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1455300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1636000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1525700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1454700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1511000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1467400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1354400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1262700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1233500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1284300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1247800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1279200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1270300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1152400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1057100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1024300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>970300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1025400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>964100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>861300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>834400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>851100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>853000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>836200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>820400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>795100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>779700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>776800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>769400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>696600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>695400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>680100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>652800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>633700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>432100</v>
+      </c>
+      <c r="E9" s="3">
         <v>381500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>389100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>405400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>334200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>310700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>261400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>308200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>276200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>286900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>266000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>273600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>249400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>237700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>236000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>282700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>271200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>252800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>257000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>234700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>205100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>214000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>208000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>224500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>193000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>184300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>192900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>182700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>186600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>190700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>192900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>190600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>185400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>178800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>181200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>166900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>169500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>162000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>155700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2044700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1894500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2019700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1849400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1405500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1293600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1193900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1327800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1249600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1167800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1245000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1193800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1105000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1025000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>997500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1001600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>976600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1026400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1013300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>917700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>852000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>810300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>762300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>800900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>771100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>677000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>641500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>668400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>666400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>645500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>627500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>604500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>594300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>598000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>588200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>529700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>525900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>518100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>497100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>491500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,130 +1242,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>719700</v>
+      </c>
+      <c r="E12" s="3">
         <v>700100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>715000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>746800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>625300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>554000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>553200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>554800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>508900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>493100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>525500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>465800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>484500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>460500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>439200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>461600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>444800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>390000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>384000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>413900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>371100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>362300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>357500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>339600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>322600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>302600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>314300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>290500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>284800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>290300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>271300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>290900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>277400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>252100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>264400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>244500</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>228700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>223000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>212600</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>222000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1474,225 +1490,231 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-423200</v>
+      </c>
+      <c r="E14" s="3">
         <v>115900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>118300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-548900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-49000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>51600</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N14" s="3">
         <v>-55100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>21900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>18300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>29700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>13400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-18300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>11000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>2200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>5500</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>6000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>12900</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>12100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>402400</v>
+      </c>
+      <c r="E15" s="3">
         <v>403600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>404200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>405200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>74900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>8600</v>
       </c>
       <c r="W15" s="3">
         <v>8600</v>
       </c>
       <c r="X15" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Y15" s="3">
         <v>8300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>9900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9400</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>10100</v>
       </c>
       <c r="AE15" s="3">
         <v>10100</v>
       </c>
       <c r="AF15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>10300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>10800</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>10700</v>
       </c>
       <c r="AI15" s="3">
         <v>10700</v>
@@ -1701,25 +1723,28 @@
         <v>10700</v>
       </c>
       <c r="AK15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="AL15" s="3">
         <v>9500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>7800</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>7900</v>
       </c>
       <c r="AN15" s="3">
         <v>7900</v>
       </c>
       <c r="AO15" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AP15" s="3">
         <v>8000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1759,252 +1784,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2039700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2087500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2133500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1574500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1227800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1203500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1271700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1165500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1122600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1158400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1044600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1032400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>975900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>976900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1066900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1013800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>915500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>923200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>962100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>855200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>830100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>822000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>829300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>753500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>735400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>746900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>721400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>725400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>720700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>673000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>733600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>715700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>649800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>661700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>604900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>590000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>626500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>555900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>551000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>359700</v>
+      </c>
+      <c r="E18" s="3">
         <v>236300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>321300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>121400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>165300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>376400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>251800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>364300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>360200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>332100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>352600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>422800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>322000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>286800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>256600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>217400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>234000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>363700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>347100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>190300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>201900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>194200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>148300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>196100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>210600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>125900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>87500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>129700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>127600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>115500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>147400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>61500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>127000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>107700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>91700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>105400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>53600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>96900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>82700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2047,287 +2079,294 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-40300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>24700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-14700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-27800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-37900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>29900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>23200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-19300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>22600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>29500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>27200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>13600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>22300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>15300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>10100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>9700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>10200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>12800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>777800</v>
+      </c>
+      <c r="E21" s="3">
         <v>659300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>746900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>546900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>280500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>363300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>279100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>381700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>406600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>355000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>407200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>408800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>348900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>295600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>337100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>271200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>294500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>390500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>389400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>252500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>265300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>266200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>228500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>243100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>291900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>164900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>153400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>182200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>184400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>188800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>203400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>115500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>129900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>176100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>166900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>147100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>162200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>111500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>159100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>133000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E22" s="3">
         <v>133400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>162700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>194800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>146500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>94300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -2339,7 +2378,7 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
@@ -2348,317 +2387,326 @@
         <v>400</v>
       </c>
       <c r="U22" s="3">
+        <v>400</v>
+      </c>
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>800</v>
       </c>
       <c r="X22" s="3">
         <v>800</v>
       </c>
       <c r="Y22" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z22" s="3">
         <v>700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>2800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>1800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>2300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>1900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>683900</v>
+      </c>
+      <c r="E23" s="3">
         <v>19300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>79100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>516500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>189300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>396200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>291100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>322900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>392000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>341500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>457500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>403800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>325600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>296600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>279600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>212100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>236400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>339800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>327200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>199100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>213300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>216000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>177100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>191600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>236900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>110200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>99600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>131600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>132900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>133900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>147100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>52200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>71900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>119300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>120100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>99900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>112800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>62000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>108400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>82800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-53000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>47200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>62100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-30700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>22900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>23900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>16700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>45900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>15100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>33000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-197100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>16800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>220000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>8700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>21800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2779,252 +2827,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>545700</v>
+      </c>
+      <c r="E26" s="3">
         <v>16900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>64700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>448500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>242300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>349000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>297400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>260800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>422700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>296100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>434500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>343400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>332500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>272600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>266800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>151600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>219600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>293900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>313300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>201100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>198400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>194800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>162000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>196600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>252900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>109900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>104100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>160700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>99900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>118200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>153500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>249300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>102500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>115300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-120100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>116800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>53300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>86600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>545800</v>
+      </c>
+      <c r="E27" s="3">
         <v>17100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>448700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>242500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>345300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>295700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1114100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>408100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>292100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>449100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>349200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>336300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>272900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>269700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>153500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>222600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>294800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>313700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>201400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>198600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>195100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>162300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>197500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>252900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>109900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>104100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>160700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>99900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>118200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>153500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>249300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>102500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>115300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-120100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>116800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>53300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>86600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3145,8 +3202,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3163,37 +3223,37 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-3900</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>834800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-17800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-7000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>11700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>3100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1900</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>24</v>
@@ -3204,8 +3264,8 @@
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -3222,8 +3282,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -3240,20 +3300,20 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="3">
         <v>5000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-119000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3267,8 +3327,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3389,8 +3452,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3511,252 +3577,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E32" s="3">
         <v>19300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>40300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-24700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>14700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>27800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>37900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-29900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-23200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>19300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-13600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-22300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-12500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-15300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-10100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-9700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-10200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-12800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>545800</v>
+      </c>
+      <c r="E33" s="3">
         <v>17100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>65000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>448700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>242500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>345300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>295700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1114100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>408100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>292100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>449100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>349200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>336300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>272900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>271500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>153500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>222600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>294800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>313700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>201400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>198600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>195100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>162300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>197500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>252900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>109900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>104100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>160700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>99900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>118200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>153500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>254300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>102500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-120100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>116800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>53300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>86600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3877,257 +3952,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>545800</v>
+      </c>
+      <c r="E35" s="3">
         <v>17100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>65000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>448700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>242500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>345300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>295700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1114100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>408100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>292100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>449100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>349200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>336300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>272900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>271500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>153500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>222600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>294800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>313700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>201400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>198600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>195100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>162300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>197500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>252900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>109900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>104100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>160700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>99900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>118200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>153500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>254300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>102500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-120100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>116800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>53300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>86600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4170,8 +4254,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4214,195 +4299,199 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3606300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2412500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2129600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2888000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2526500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14119100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3653900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3896500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1839800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1502900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1118900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1434000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1686100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1544600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1154900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1417600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1383600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1573600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1124300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1432800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1385400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1457900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1023100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1235700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1049900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>856400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>700400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>728600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>686800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>631200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>592300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>723100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>741200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>570800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>605900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1048400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1155000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>991300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>827700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>976600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E42" s="3">
         <v>72000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>72900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>67200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>144800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>155500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>153900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>154400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>156800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>154500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>151600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>148400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>150800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>147100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>147900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>147600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>146900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>147700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>147900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>144800</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>24</v>
@@ -4419,8 +4508,8 @@
       <c r="AC42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -4440,246 +4529,252 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
-      <c r="AK42" s="3" t="s">
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
-      </c>
       <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
         <v>147500</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>140200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>138600</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>140700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2184800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1295900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2416300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2391100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2214300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1900300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1723100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1691500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1499100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1365900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1533100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>856700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>936700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1029100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1294500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1056600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>963200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>958700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1312800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>885500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>860400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>887900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1032200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1027600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>876000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>847300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1026700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>578800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>487100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>586500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>817800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>630700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>545700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>615300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>543600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>499400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>467000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>429300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>386600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>479100</v>
+      </c>
+      <c r="E44" s="3">
         <v>441800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>393200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>365200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>382100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>395300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>415200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>361800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>386000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>377900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>382700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>325600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>282800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>256400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>220900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>211900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>219700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>213500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>212900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>229000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>241100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>230100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>230900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>192300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>159800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>166400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>148100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>141500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>155100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>166300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>137600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>122400</v>
-      </c>
-      <c r="AI44" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AJ44" s="3" t="s">
         <v>24</v>
@@ -4693,8 +4788,8 @@
       <c r="AM44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AN44" s="3">
-        <v>0</v>
+      <c r="AN44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AO44" s="3">
         <v>0</v>
@@ -4702,263 +4797,272 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E45" s="3">
         <v>118100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>109800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>109000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>44400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1042200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1039300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>128100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>211100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>178600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>185000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>181500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>149800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>113000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>132300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>113900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>111500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>93600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>100300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>90600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>76400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>290100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>288600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>259800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>249900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>67500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>178600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>184100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>182800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>134800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>125100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>121200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>131100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>104700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6644300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5437200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5373600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6012100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5595600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16879000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6323600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6469700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5127800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4653100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3407900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3430600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3268300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3160900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3028400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3012700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2899000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3074200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2947500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2808300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2764000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2689800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2397700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2549200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2186000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1960800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1951400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1738900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1617600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1643900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1797600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1543800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1465600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1370200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1332300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1682600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1894600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1682000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1484000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1716900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>700</v>
+      </c>
+      <c r="E47" s="3">
         <v>500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>900</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>24</v>
@@ -4990,8 +5094,8 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5068,252 +5172,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1444200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1411900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1390300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1398700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1393100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1157700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1092300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1128900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1128000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1094800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1118500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1109800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1110700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1123200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1103800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1042400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1061400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1076700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>959000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>965600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>964000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>984200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>948700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>949600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>956800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>933200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>917700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>429500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>372600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>344200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>317900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>309300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>290400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>283800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>284400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>266000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>262000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>259500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>256800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>257000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>38293400</v>
+      </c>
+      <c r="E49" s="3">
         <v>38729200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>39170400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39578800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40025600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3634700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3614300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3644000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3710400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3704300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4508800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3585600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4224600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4245400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4226000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4228700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4259500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3949500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3853600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3854900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3735200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3666400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3687400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3619400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3631700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3590600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3513700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3450600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3426400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3450700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3477900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3503700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3533200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3569300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3565100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2960800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2909000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2936100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2954200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2784900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5434,8 +5547,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5556,130 +5672,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>792400</v>
+      </c>
+      <c r="E52" s="3">
         <v>749600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>731400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>707200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>696500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>508900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>552600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>510900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>509200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>485700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>480100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1286300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>409100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>388900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1207400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1134300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1109600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1109900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1141200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1123400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1022700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>999200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>979000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>911800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>888700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>838000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>820100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>786200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>736800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>755400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>751100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>789200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>506000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>475800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>535600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>487000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>613300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>588900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>569200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>481500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5800,130 +5922,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47726300</v>
+      </c>
+      <c r="E54" s="3">
         <v>46889000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47237900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48224500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48230300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23756500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13041100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13073600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11648700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11011800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10558300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10333100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9923200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9790700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9565600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9418100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9329500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9210400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8901300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8752300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8485900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8339600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8012800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8030100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7663300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7322500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7202900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6405200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6153400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6194200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6344500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6146000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5795200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5699100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5717500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5396400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5678900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5466600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5264300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>5240400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5966,8 +6094,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6010,175 +6139,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>187300</v>
+      </c>
+      <c r="E57" s="3">
         <v>179300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>113300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>164800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>132900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>84700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>207300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>78500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>92300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>76800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>154600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>84400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>70200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>72000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>74500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>27400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>44100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>30000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>37100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>51800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>26600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>31200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>26000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>85000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>49500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>43500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>42100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>20000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>19900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>33500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>23800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1158100</v>
+      </c>
+      <c r="E58" s="3">
         <v>157600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>155200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>150300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>149600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>99300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>94800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>89900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>84600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>89200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>79800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>80200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>78100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6192,558 +6325,573 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>75000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>82500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>89900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>97400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>27100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>24200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>121400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>208600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>165700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>414700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>343800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>497800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>396800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>440900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>9900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>298000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>278000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>177000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>205000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2419600</v>
+      </c>
+      <c r="E59" s="3">
         <v>2492800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2594300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2340600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2028500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1495000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1564600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1538900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1691300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1805100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1980100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2072500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1914300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1979700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2654800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2736900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2473900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2388200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2442500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2311100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2210900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2121600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2048600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2082800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1994900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1881000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1820600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1715000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1599000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1536000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1584900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1673600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1536100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1441600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1467400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1584200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1446500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1281800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1255700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1496200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4969900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3790600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3942700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3722500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3444200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2406100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2358600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2650100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2535000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2508400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2644500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2985500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2730000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2748700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2725000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2774500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2545900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2462700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2471700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2413500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2334600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2255700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2171400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2139900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2056300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2054200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2055700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1752500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1630500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1732900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2025600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2102400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2083400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1881900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1950400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1614100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1764400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1593300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1456600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1714900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9683700</v>
+      </c>
+      <c r="E61" s="3">
         <v>10684300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10713300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14143100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14990700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10615100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>565700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>589700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>584000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>560200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>580800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>597800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>609000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>611900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>24400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>25600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>25700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>100800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>107100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>114400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>122500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>120100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>125300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>126200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>127100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>125500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>123800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>127500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>131300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>134100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>137800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>139700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>142500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>687100</v>
+      </c>
+      <c r="E62" s="3">
         <v>669800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>658900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>648200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>608900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>488600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>495700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>433200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>465200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>446500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>436500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>414800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>389500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>365900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1141300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1063600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1110100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1113000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1015100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1014700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>971400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>965700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>928900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>877000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>898600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>873000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>870000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>443700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>458000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>419700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>407000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>433000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>424100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>429300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>495300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>368500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>353600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>356000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>340500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>330300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6864,8 +7012,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6986,8 +7137,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7108,130 +7262,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16574900</v>
+      </c>
+      <c r="E66" s="3">
         <v>16412000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16689900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19897400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20616100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13840900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3736200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4050400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3903300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3823000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3851600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4148800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3923400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3917900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3928900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3902400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3725500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3646100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3514600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3457100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3334900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3251400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3130600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3122700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3067300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3047400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3054100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2322100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2219600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2284700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2565700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2666800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2637100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2442800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2581000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2120800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2255800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2089100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1939600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2045200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7274,8 +7434,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7396,8 +7557,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7518,8 +7682,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7640,8 +7807,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7762,130 +7932,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10943400</v>
+      </c>
+      <c r="E72" s="3">
         <v>10397600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10380400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10315500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9866800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9624300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9279000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8984100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7884000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7478400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7188600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6741700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6389800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6075000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5805800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5534300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5377600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5157600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4863400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4549700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4348300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4149600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3954500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3795400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3597900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3356500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3268200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3164100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3003400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2912800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2820900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2543700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2296500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2223300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2133900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2143900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2277500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2170100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2137400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1947600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8006,8 +8182,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8128,8 +8307,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8250,130 +8432,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31152500</v>
+      </c>
+      <c r="E76" s="3">
         <v>30478100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>30548800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>28327600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27614500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9915700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9304800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8990700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7709400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7153200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6671000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6147300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5958600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5831900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5636800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5515700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5604000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5564300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5386800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5295100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5151000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5088100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4882300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4907400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4595900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4275100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4148800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4083000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3933800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3909600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3778800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3479200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3158100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3256300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3136500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3275600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3423200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3377500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3324700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3195100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8494,257 +8682,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>545800</v>
+      </c>
+      <c r="E81" s="3">
         <v>17100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>65000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>448700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>242500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>345300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>295700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1114100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>408100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>292100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>449100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>349200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>336300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>272900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>271500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>153500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>222600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>294800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>313700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>201400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>198600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>195100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>162300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>197500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>252900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>109900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>104100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>160700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>99900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>118200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>153500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>254300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>79400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>102500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-120100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>116800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>53300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>86600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8787,130 +8984,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E83" s="3">
         <v>37200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>35300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>54100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>48000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>49500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>56400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>28200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>57300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>58700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>57700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>50300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>61700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>52400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>51200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>50600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>50800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>54100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>52800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>49300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>51800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>59000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>53400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>52900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>45300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>47100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>47600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>49500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>49200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9031,8 +9232,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9153,8 +9357,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9275,8 +9482,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9397,8 +9607,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9519,130 +9732,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>812800</v>
+      </c>
+      <c r="E89" s="3">
         <v>628900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>856800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>639700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>671000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>275400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-67500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>562800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>455400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>476600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-87800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>326100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>559500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>702900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>114800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>393500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>439700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>750000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>155700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>370600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>421800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>526300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>174000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>202200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>399400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>379900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>9800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>221200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>370500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>352800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-144000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>130900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>289200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>63400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-59100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>184900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>279900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>123000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>46900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>147700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9685,130 +9904,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-53100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-44100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-40200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-343700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-115300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-62200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-159200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-112600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-54600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-75800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-53400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-206800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-19800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9929,8 +10152,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10051,130 +10277,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>443100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-52900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>564400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16499700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>76000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1443000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-53800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-111800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-53800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-91500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-41300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-345300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-118000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-68000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-163200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-265100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-103500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-88200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-133600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-117600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-52000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-37600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-26100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-54800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-625000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>55700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-26500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-202800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-17100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10217,8 +10449,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10261,8 +10494,8 @@
       <c r="P96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10339,8 +10572,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10461,8 +10697,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10583,8 +10822,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10705,370 +10947,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-281000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1583200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-835900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4237000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10096400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-141800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>30100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-187200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-254300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-351400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-214400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-376800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-291100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-266200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-164500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-394600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-159300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-225700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-70700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-293100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>10900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-130800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-114200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>93500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-59600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-264700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-275700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>38100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-104200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-83100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-38000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>230400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-347200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-92700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>51000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>15900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-101300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>17900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>35700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-27100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-18200</v>
       </c>
       <c r="P101" s="3">
         <v>-18200</v>
       </c>
       <c r="Q101" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="R101" s="3">
         <v>35700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-27100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-18200</v>
       </c>
       <c r="T101" s="3">
         <v>-18200</v>
       </c>
       <c r="U101" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-3500</v>
       </c>
       <c r="X101" s="3">
         <v>-3500</v>
       </c>
       <c r="Y101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="Z101" s="3">
         <v>10000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>13100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>11600</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>3100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>5300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1194000</v>
+      </c>
+      <c r="E102" s="3">
         <v>282400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-759400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>361600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11591300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10465700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-240900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2039200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>347800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>390500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-320000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-246800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>141600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>389100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-262600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-190000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>449300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-308600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>47400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-72500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>434800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-212600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>186000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>193600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>156100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-28200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>41800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>55600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>38800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-130800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>170400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-35200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-442200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-106600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>163700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>163600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-148900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>30300</v>
       </c>
     </row>
